--- a/قائمة الوحدات الخاصة بالفوج20252026/قائمة جهة نابل فوج قرمبالية المدينة وحدة الياسمين.xlsx
+++ b/قائمة الوحدات الخاصة بالفوج20252026/قائمة جهة نابل فوج قرمبالية المدينة وحدة الياسمين.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>المعرف</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>مشترك</t>
+  </si>
+  <si>
+    <t>code_unite</t>
+  </si>
+  <si>
+    <t>ZHRT</t>
   </si>
 </sst>
 </file>
@@ -456,6 +462,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -482,8 +491,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>21</v>
       </c>
       <c r="B2">
         <v>900007686</v>
@@ -511,8 +520,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>21</v>
       </c>
       <c r="B3">
         <v>900011091</v>
@@ -540,8 +549,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
+      <c r="A4" t="s">
+        <v>21</v>
       </c>
       <c r="B4">
         <v>900016675</v>
@@ -571,7 +580,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A2:I3 A4:I4" numberStoredAsText="1"/>
+    <ignoredError sqref="B1:I1 B3:I3 B4:I4 B2:I2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>